--- a/employee_surveys/012_nonprofit_employee_burnout_study--employee_surveys.xlsx
+++ b/employee_surveys/012_nonprofit_employee_burnout_study--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>physical_health_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,17 +2180,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>physical_health_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -2202,444 +2202,444 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mental_health_choices</t>
+          <t>sleep_quality_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>mental_health_choices</t>
+          <t>sleep_quality_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mental_health_choices</t>
+          <t>sleep_quality_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mental_health_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Extremely High</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>extremely_low</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Extremely Low</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>job_leadership_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Supportive</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_leadership_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>demanding</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Demanding</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_leadership_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_culture_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_culture_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Extremely High</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_culture_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>extremely_low</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Extremely Low</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>job_leadership_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>supportive</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Supportive</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>job_leadership_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>demanding</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Demanding</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>job_leadership_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Neither</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>job_culture_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Extremely High</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>job_culture_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>extremely_low</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Extremely Low</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>job_culture_choices</t>
+          <t>burnout_factors_score_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>burnout_factors_score_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>2-3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>burnout_factors_score_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>4-5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>burnout_factors_score_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>6-7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>burnout_factors_score_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Extremely High</t>
+          <t>8-9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>burnout_factors_score_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>extremely_low</t>
+          <t>10-11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Extremely Low</t>
+          <t>10-11</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>burnout_factors_score_choices</t>
+          <t>burnout_symptoms_score_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>burnout_factors_score_choices</t>
+          <t>burnout_symptoms_score_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>burnout_factors_score_choices</t>
+          <t>burnout_symptoms_score_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>burnout_factors_score_choices</t>
+          <t>burnout_symptoms_score_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>burnout_factors_score_choices</t>
+          <t>burnout_symptoms_score_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>burnout_factors_score_choices</t>
+          <t>burnout_symptoms_score_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>burnout_symptoms_score_choices</t>
+          <t>physical_health_score_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>burnout_symptoms_score_choices</t>
+          <t>physical_health_score_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>burnout_symptoms_score_choices</t>
+          <t>physical_health_score_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>burnout_symptoms_score_choices</t>
+          <t>physical_health_score_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2809,7 +2809,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>burnout_symptoms_score_choices</t>
+          <t>physical_health_score_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2826,7 +2826,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>burnout_symptoms_score_choices</t>
+          <t>physical_health_score_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>physical_health_score_choices</t>
+          <t>mental_health_score_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>physical_health_score_choices</t>
+          <t>mental_health_score_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>physical_health_score_choices</t>
+          <t>mental_health_score_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2894,7 +2894,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>physical_health_score_choices</t>
+          <t>mental_health_score_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>physical_health_score_choices</t>
+          <t>mental_health_score_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>physical_health_score_choices</t>
+          <t>mental_health_score_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mental_health_score_choices</t>
+          <t>burnout_prevalence_score_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>mental_health_score_choices</t>
+          <t>burnout_prevalence_score_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mental_health_score_choices</t>
+          <t>burnout_prevalence_score_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>mental_health_score_choices</t>
+          <t>burnout_prevalence_score_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>mental_health_score_choices</t>
+          <t>burnout_prevalence_score_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>mental_health_score_choices</t>
+          <t>burnout_prevalence_score_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>burnout_prevalence_score_choices</t>
+          <t>job_satisfaction_score_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>burnout_prevalence_score_choices</t>
+          <t>job_satisfaction_score_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>burnout_prevalence_score_choices</t>
+          <t>job_satisfaction_score_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>burnout_prevalence_score_choices</t>
+          <t>job_satisfaction_score_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>burnout_prevalence_score_choices</t>
+          <t>job_satisfaction_score_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>burnout_prevalence_score_choices</t>
+          <t>job_satisfaction_score_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>job_satisfaction_score_choices</t>
+          <t>sleep_quality_score_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>job_satisfaction_score_choices</t>
+          <t>sleep_quality_score_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>job_satisfaction_score_choices</t>
+          <t>sleep_quality_score_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>job_satisfaction_score_choices</t>
+          <t>sleep_quality_score_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3217,7 +3217,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>job_satisfaction_score_choices</t>
+          <t>sleep_quality_score_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>job_satisfaction_score_choices</t>
+          <t>sleep_quality_score_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>sleep_quality_score_choices</t>
+          <t>physical_health_score_average_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sleep_quality_score_choices</t>
+          <t>physical_health_score_average_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sleep_quality_score_choices</t>
+          <t>physical_health_score_average_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sleep_quality_score_choices</t>
+          <t>physical_health_score_average_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sleep_quality_score_choices</t>
+          <t>physical_health_score_average_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>sleep_quality_score_choices</t>
+          <t>physical_health_score_average_choices</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>physical_health_score_average_choices</t>
+          <t>mental_health_score_average_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>physical_health_score_average_choices</t>
+          <t>mental_health_score_average_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>physical_health_score_average_choices</t>
+          <t>mental_health_score_average_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>physical_health_score_average_choices</t>
+          <t>mental_health_score_average_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>physical_health_score_average_choices</t>
+          <t>mental_health_score_average_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>physical_health_score_average_choices</t>
+          <t>mental_health_score_average_choices</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mental_health_score_average_choices</t>
+          <t>wellbeing_score_average_choices</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mental_health_score_average_choices</t>
+          <t>wellbeing_score_average_choices</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>mental_health_score_average_choices</t>
+          <t>wellbeing_score_average_choices</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>mental_health_score_average_choices</t>
+          <t>wellbeing_score_average_choices</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>mental_health_score_average_choices</t>
+          <t>wellbeing_score_average_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mental_health_score_average_choices</t>
+          <t>wellbeing_score_average_choices</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3549,108 +3549,6 @@
         </is>
       </c>
       <c r="C144" t="inlineStr">
-        <is>
-          <t>10-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>wellbeing_score_average_choices</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>wellbeing_score_average_choices</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>wellbeing_score_average_choices</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>wellbeing_score_average_choices</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>6-7</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>6-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>wellbeing_score_average_choices</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>8-9</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>8-9</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>wellbeing_score_average_choices</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>10-11</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
         <is>
           <t>10-11</t>
         </is>
